--- a/currentbuild/StructureDefinition-AuditEventNorwayEncounter.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventNorwayEncounter.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.0</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T18:58:49+00:00</t>
+    <t>2024-03-12T11:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
